--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486855_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486855_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9338</v>
+        <v>3.4912</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1349</v>
+        <v>1.7923</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7989</v>
+        <v>1.6989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0625</v>
+        <v>2.7144</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7138</v>
+        <v>-2.1507</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7763</v>
+        <v>4.865</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6926</v>
+        <v>2.4976</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3378</v>
+        <v>-1.7383</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3549</v>
+        <v>4.2359</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6302</v>
+        <v>0.2167</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0516</v>
+        <v>-0.4124</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5786</v>
+        <v>0.6291</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8748</v>
+        <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0849</v>
+        <v>-1.2766</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2903</v>
+        <v>-0.7053</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7945</v>
+        <v>-0.5713</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.312</v>
+        <v>3.0624</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3178</v>
+        <v>2.8607</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0058</v>
+        <v>0.2017</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5697</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1692</v>
+        <v>-0.0804</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6274</v>
+        <v>0.1703</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4582</v>
+        <v>-0.2507</v>
       </c>
       <c r="V3" t="n">
         <v>1.6591</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9856</v>
+        <v>2.9884</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5831</v>
+        <v>1.7823</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4024</v>
+        <v>1.2061</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7144</v>
+        <v>0.0625</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1507</v>
+        <v>-0.7138</v>
       </c>
       <c r="I4" t="n">
-        <v>4.865</v>
+        <v>0.7763</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4976</v>
+        <v>1.6926</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7383</v>
+        <v>0.3378</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2359</v>
+        <v>1.3549</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2167</v>
+        <v>-1.6302</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4124</v>
+        <v>-1.0516</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6291</v>
+        <v>-0.5786</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0534</v>
+        <v>2.8748</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7822</v>
+        <v>0.1395</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9145</v>
+        <v>-0.0622</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8677</v>
+        <v>0.2017</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3695</v>
+        <v>2.6026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8117</v>
+        <v>1.4006</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5578</v>
+        <v>1.202</v>
       </c>
       <c r="G5" t="n">
         <v>0.8932</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7014</v>
+        <v>-0.1125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6233</v>
+        <v>0.2675</v>
       </c>
       <c r="V5" t="n">
         <v>0.9384</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7601</v>
+        <v>1.3608</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5661</v>
+        <v>2.6707</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.806</v>
+        <v>-1.3099</v>
       </c>
       <c r="G6" t="n">
         <v>0.8406</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6444</v>
+        <v>0.2451</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.248</v>
+        <v>-0.1434</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8924</v>
+        <v>0.3885</v>
       </c>
       <c r="V6" t="n">
         <v>0.4805</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.284</v>
+        <v>0.3607</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.192</v>
+        <v>-0.0215</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.092</v>
+        <v>0.3823</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3448</v>
@@ -1000,13 +1000,13 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2143</v>
+        <v>-0.5696</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1358</v>
+        <v>0.0347</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0785</v>
+        <v>-0.6042</v>
       </c>
       <c r="V7" t="n">
         <v>1.0698</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3283</v>
+        <v>-0.093</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0155</v>
+        <v>-0.0012</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3438</v>
+        <v>-0.0917</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3122</v>
+        <v>-1.1274</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8199</v>
+        <v>-1.288</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5077</v>
+        <v>0.1605</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7905</v>
+        <v>-0.315</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0668</v>
+        <v>-0.9859</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2763</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4783</v>
+        <v>-0.8124</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2468</v>
+        <v>-0.302</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2314</v>
+        <v>-0.5104</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3328</v>
+        <v>-0.1976</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2517</v>
+        <v>-0.1667</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.0309</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3722</v>
+        <v>-0.3164</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9265</v>
+        <v>0.11</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5543</v>
+        <v>-0.4264</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5763</v>
+        <v>-1.0554</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.489</v>
+        <v>-1.0738</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9127</v>
+        <v>0.0184</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0147</v>
+        <v>-0.0139</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1294</v>
+        <v>-0.6584</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1441</v>
+        <v>0.6445</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.591</v>
+        <v>-1.0415</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3596</v>
+        <v>-0.4154</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2314</v>
+        <v>-0.6261</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>0.122</v>
+        <v>-0.2877</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1122</v>
+        <v>-0.1163</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0098</v>
+        <v>-0.1714</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4646</v>
+        <v>-0.6059</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>-0.2325</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5746</v>
+        <v>-0.3734</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0554</v>
+        <v>0.3122</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0738</v>
+        <v>1.8199</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0184</v>
+        <v>-1.5077</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0139</v>
+        <v>0.7905</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6584</v>
+        <v>2.0668</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6445</v>
+        <v>-1.2763</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0415</v>
+        <v>-0.4783</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4154</v>
+        <v>-0.2468</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6261</v>
+        <v>-0.2314</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4359</v>
+        <v>0.0552</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1163</v>
+        <v>0.0038</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3196</v>
+        <v>0.0514</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.63</v>
+        <v>-0.6424</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4197</v>
+        <v>-1.3449</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2103</v>
+        <v>0.7025</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1274</v>
+        <v>-0.5763</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.288</v>
+        <v>-1.489</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1605</v>
+        <v>0.9127</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.315</v>
+        <v>1.0147</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9859</v>
+        <v>-0.1294</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.1441</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8124</v>
+        <v>-1.591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.302</v>
+        <v>-1.3596</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5104</v>
+        <v>-0.2314</v>
       </c>
       <c r="P11" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7346</v>
+        <v>-0.1482</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5851</v>
+        <v>-0.3062</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1495</v>
+        <v>0.158</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4805</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2571</v>
+        <v>-0.8544</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3058</v>
+        <v>0.008</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9514</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.517</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8202</v>
+        <v>-0.4175</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0298</v>
+        <v>0.0592</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7679</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.0248</v>
+        <v>11.354</v>
       </c>
       <c r="E13" t="n">
-        <v>8.6951</v>
+        <v>9.0245</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3295</v>
+        <v>2.3297</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6323</v>
+        <v>0.6322999999999998</v>
       </c>
       <c r="H13" t="n">
         <v>-4.5906</v>
       </c>
       <c r="I13" t="n">
-        <v>5.222499999999999</v>
+        <v>5.2225</v>
       </c>
       <c r="J13" t="n">
         <v>12.0019</v>
@@ -1456,7 +1456,7 @@
         <v>-8.017099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.3528</v>
+        <v>-3.352799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>10.2671</v>
@@ -1468,16 +1468,16 @@
         <v>18.4809</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7121</v>
+        <v>-2.3828</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.21</v>
+        <v>-1.8805</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5022000000000001</v>
+        <v>-0.5021999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8379</v>
+        <v>2.837899999999999</v>
       </c>
       <c r="W13" t="n">
         <v>7.1168</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6281</v>
+        <v>4.8943</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0692</v>
+        <v>3.8846</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5589</v>
+        <v>1.0097</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6959</v>
+        <v>2.3717</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0486</v>
+        <v>2.0824</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.2893</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5107</v>
+        <v>3.1366</v>
       </c>
       <c r="K14" t="n">
-        <v>0.419</v>
+        <v>1.966</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0916</v>
+        <v>1.1706</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8147</v>
+        <v>-0.7649</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4676</v>
+        <v>0.1164</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3472</v>
+        <v>-0.8813</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9938</v>
+        <v>0.7012</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4066</v>
+        <v>-0.0815</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="V14" t="n">
-        <v>2.117</v>
+        <v>0.5893</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3573</v>
+        <v>0.8295</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2402</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1481</v>
+        <v>4.7588</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6754</v>
+        <v>4.0692</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4727</v>
+        <v>0.6896</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3717</v>
+        <v>0.6959</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0824</v>
+        <v>-0.0486</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2893</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1366</v>
+        <v>1.5107</v>
       </c>
       <c r="K15" t="n">
-        <v>1.966</v>
+        <v>0.419</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1706</v>
+        <v>1.0916</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7649</v>
+        <v>-0.8147</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1164</v>
+        <v>-0.4676</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8813</v>
+        <v>-0.3472</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.045</v>
+        <v>1.1245</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2907</v>
+        <v>0.4066</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2458</v>
+        <v>0.7179</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5893</v>
+        <v>2.117</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8295</v>
+        <v>2.3573</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2402</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.0658</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.9364</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1452</v>
+        <v>0.1294</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.516</v>
+        <v>1.1897</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9925</v>
+        <v>1.7579</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5234</v>
+        <v>-0.5682</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4169</v>
+        <v>2.4359</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4959</v>
+        <v>1.7519</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0789</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.099</v>
+        <v>-1.2462</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4967</v>
+        <v>0.006</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.2522</v>
       </c>
       <c r="P16" t="n">
         <v>-0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9759</v>
+        <v>0.2868</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8672</v>
+        <v>-0.2674</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1087</v>
+        <v>0.5542</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8067</v>
+        <v>-0.7468</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9994</v>
+        <v>0.8488</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1927</v>
+        <v>-1.5956</v>
       </c>
       <c r="G17" t="n">
         <v>0.6381</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5793</v>
+        <v>1.0258</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5651</v>
+        <v>0.4144</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0142</v>
+        <v>0.6113</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1786</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.501</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4134</v>
+        <v>-1.1967</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0876</v>
+        <v>0.4371</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1897</v>
+        <v>-0.8002</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7579</v>
+        <v>-0.0002</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5682</v>
+        <v>-0.8</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4359</v>
+        <v>-0.0614</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7519</v>
+        <v>0.1363</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.1977</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2462</v>
+        <v>-0.7388</v>
       </c>
       <c r="N18" t="n">
-        <v>0.006</v>
+        <v>-0.1365</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2522</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.278</v>
+        <v>0.246</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7905</v>
+        <v>-0.1086</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5124</v>
+        <v>0.3546</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4593</v>
+        <v>-0.8351</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9062</v>
+        <v>-0.696</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5532</v>
+        <v>-0.1391</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6104000000000001</v>
+        <v>-1.516</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9181</v>
+        <v>-0.9925</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3077</v>
+        <v>-0.5234</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8727</v>
+        <v>-0.4169</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8332</v>
+        <v>-0.4959</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2623</v>
+        <v>-1.099</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9151</v>
+        <v>-0.4967</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3472</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.6694</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5997</v>
+        <v>1.3318</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.5074</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3998</v>
+        <v>0.8244</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6982</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5061</v>
+        <v>-1.2176</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5339</v>
+        <v>1.6209</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0279</v>
+        <v>-2.8386</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3677</v>
+        <v>-0.2023</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.0839</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6736</v>
+        <v>-0.1184</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3363</v>
+        <v>1.3727</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.639</v>
+        <v>0.9125</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6974</v>
+        <v>0.4602</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0314</v>
+        <v>-1.575</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0552</v>
+        <v>-0.9964</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0238</v>
+        <v>-0.5786</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1383</v>
+        <v>0.7177</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1976</v>
+        <v>0.2051</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0593</v>
+        <v>0.5125</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.5277</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6139</v>
+        <v>-1.4171</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6151</v>
+        <v>-1.5339</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0012</v>
+        <v>0.1168</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8002</v>
+        <v>-1.3677</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0002</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8</v>
+        <v>-0.6736</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0614</v>
+        <v>-1.3363</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1363</v>
+        <v>-0.639</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1977</v>
+        <v>-0.6974</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7388</v>
+        <v>-0.0314</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1365</v>
+        <v>-0.0552</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.0238</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6083</v>
+        <v>-0.0494</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.527</v>
+        <v>-0.1976</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0813</v>
+        <v>0.1482</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1922</v>
+        <v>-1.9544</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9933</v>
+        <v>-1.6384</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1855</v>
+        <v>-0.3161</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2023</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0839</v>
+        <v>0.9181</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1184</v>
+        <v>-0.3077</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3727</v>
+        <v>1.8727</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9125</v>
+        <v>1.8332</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4602</v>
+        <v>0.0395</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.575</v>
+        <v>-1.2623</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9964</v>
+        <v>-0.9151</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5786</v>
+        <v>-0.3472</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2053</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2569</v>
+        <v>0.1046</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4225</v>
+        <v>0.2673</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1656</v>
+        <v>-0.1626</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5277</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0698</v>
+        <v>-0.6982</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.5975</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7066</v>
+        <v>-2.9468</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2785</v>
+        <v>-2.3044</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4281</v>
+        <v>-0.6424</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3275</v>
+        <v>-1.3302</v>
       </c>
       <c r="H23" t="n">
-        <v>0.188</v>
+        <v>0.0197</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1395</v>
+        <v>-1.3499</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0195</v>
+        <v>0.8418</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0195</v>
+        <v>0.2896</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.5522</v>
       </c>
       <c r="M23" t="n">
-        <v>0.308</v>
+        <v>-2.172</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1686</v>
+        <v>-0.2699</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1395</v>
+        <v>-1.902</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2321</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4448</v>
+        <v>0.2315</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0659</v>
+        <v>-0.1009</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3789</v>
+        <v>0.3324</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9221</v>
+        <v>-3.5078</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.455</v>
+        <v>-1.2785</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4671</v>
+        <v>-2.2294</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3302</v>
+        <v>0.3275</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0197</v>
+        <v>0.188</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3499</v>
+        <v>0.1395</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8418</v>
+        <v>0.0195</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2896</v>
+        <v>0.0195</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5522</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.172</v>
+        <v>0.308</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2699</v>
+        <v>0.1686</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.902</v>
+        <v>0.1395</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8481</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4374</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7438</v>
+        <v>-0.246</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2516</v>
+        <v>-0.0659</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4923</v>
+        <v>-0.1801</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5174</v>
+        <v>-5.5689</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3553</v>
+        <v>-5.0415</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1621</v>
+        <v>-0.5274</v>
       </c>
       <c r="G25" t="n">
         <v>-1.249</v>
@@ -2404,13 +2404,13 @@
         <v>0.2053</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9213</v>
+        <v>0.0271</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7905</v>
+        <v>-0.4767</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1309</v>
+        <v>0.5038</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2402</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.0247</v>
+        <v>-8.235199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3295</v>
+        <v>-2.329499999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.695200000000002</v>
+        <v>-5.906</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6320999999999999</v>
+        <v>-0.6320999999999998</v>
       </c>
       <c r="H26" t="n">
         <v>4.5905</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.2224</v>
+        <v>-5.222400000000001</v>
       </c>
       <c r="J26" t="n">
         <v>11.3701</v>
       </c>
       <c r="K26" t="n">
-        <v>8.017099999999997</v>
+        <v>8.017099999999999</v>
       </c>
       <c r="L26" t="n">
         <v>3.3528</v>
@@ -2467,10 +2467,10 @@
         <v>-12.002</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.4267</v>
+        <v>-3.426699999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.575199999999999</v>
+        <v>-8.575200000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-10.267</v>
@@ -2482,13 +2482,13 @@
         <v>8.213799999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7123</v>
+        <v>5.501599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5020999999999995</v>
+        <v>0.5021999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>2.21</v>
+        <v>4.9993</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8377</v>
